--- a/resources/topic/银行从业初级银行管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级银行管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R8e616ac6f362434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R4e196e7e95924b0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rd882e08b8a6c43ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rd9db74c2b678457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R61be0c57c01c4018"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rab9d3b5dbfaf42d2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36786,7 +36786,7 @@
         <x:v>https://wx.233.com/center/study/tiku/chapter?domain=ccbp&amp;subjectId=1247&amp;chapterType=1</x:v>
       </x:c>
     </x:row>
-    <x:row r="596" ht="92" customHeight="1">
+    <x:row r="596" ht="157.5" customHeight="1">
       <x:c r="A596" s="8" t="n">
         <x:v>595</x:v>
       </x:c>
@@ -36838,8 +36838,14 @@
         <x:v>A,B,C,D</x:v>
       </x:c>
       <x:c r="Q596" s="9" t="str">
-        <x:v>[图片: https://img3.233.com/2023-09/22/169537115087591.png] 
-E项（柜员离岗未退出业务操作系统，被他人利用进行操作）是“柜员管理”环节造成的操作风险，而不是“现金存取款”环节。</x:v>
+        <x:v>现金存取款环节常见的违规事项包括：
+1. 未经授权办理大额存取款业务；
+2. 未审核客户有效身份证件办理大额现金存取业务；
+3. 无支付凭证或使用商业银行内部凭证办理开户单位资金支付业务；
+4. 未能识别而收入本外币假钞或变造钞；
+5. 离岗后钱箱未加锁或虽加锁但钥匙未妥善保管；
+6. 外部人员采取化整为零手段，通过其他商业银行相互间、账户间频繁存取现金，进行洗钱活动等。
+因此，A、B、C、D项属于“现金存取款”环节的操作风险。E项（柜员离岗未退出业务操作系统，被他人利用进行操作）属于“柜员管理”环节的操作风险，不属于“现金存取款”环节。</x:v>
       </x:c>
       <x:c r="R596" s="9" t="str">
         <x:v>可查看</x:v>

--- a/resources/topic/银行从业初级银行管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级银行管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="Rc789e875fcff4882"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Rff2f6c54bf1f428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="Rcf51e75ff5bc4e6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R3a230f3692fd46b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R35c398ee69a645ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R098c0a7760484996"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -68720,7 +68720,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 00:16:21+08:00（本地时间）</x:v>
+        <x:v>2026-09-10 15:08:46+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">

--- a/resources/topic/银行从业初级银行管理_章节练习_题目整理.xlsx
+++ b/resources/topic/银行从业初级银行管理_章节练习_题目整理.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R3a230f3692fd46b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="R35c398ee69a645ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R098c0a7760484996"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部题目" sheetId="1" r:id="R832debe792ed49ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="章节统计" sheetId="2" r:id="Rb0dd2e31cc364b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="3" r:id="R2f64c2e2b2e345cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -68720,7 +68720,7 @@
         <x:v>生成时间</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>2026-09-10 15:08:46+08:00（本地时间）</x:v>
+        <x:v>2026-09-12 01:03:18+08:00（本地时间）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
